--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 8:51:54 am</t>
+    <t>28/7/2026, 10:34:37 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:34:37 am</t>
+    <t>28/7/2026, 10:42:42 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:42:42 am</t>
+    <t>28/7/2026, 10:47:45 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:47:45 am</t>
+    <t>28/7/2026, 10:59:41 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:59:41 am</t>
+    <t>28/7/2026, 11:08:32 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:08:32 am</t>
+    <t>28/7/2026, 11:12:58 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:12:58 am</t>
+    <t>28/7/2026, 11:17:42 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:17:42 am</t>
+    <t>28/7/2026, 11:28:02 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:28:02 am</t>
+    <t>28/7/2026, 11:31:49 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:31:49 am</t>
+    <t>28/7/2026, 11:38:01 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:38:01 am</t>
+    <t>28/7/2026, 11:40:44 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:40:44 am</t>
+    <t>28/7/2026, 11:43:46 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2146,7 +2146,7 @@
         <v>27</v>
       </c>
       <c r="E15" s="11">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2192,7 +2192,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3549,7 +3549,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>28</v>
@@ -3572,7 +3572,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4354,7 +4354,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6516,7 +6516,7 @@
         <v>27</v>
       </c>
       <c r="E205" s="11">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7390,7 +7390,7 @@
         <v>27</v>
       </c>
       <c r="E243" s="11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F243" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8586,7 +8586,7 @@
         <v>27</v>
       </c>
       <c r="E295" s="11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F295" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9851,7 +9851,7 @@
         <v>27</v>
       </c>
       <c r="E350" s="11">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F350" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10239,7 +10239,7 @@
         <v>27</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10285,7 +10285,7 @@
         <v>27</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11642,7 +11642,7 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
@@ -11665,7 +11665,7 @@
         <v>27</v>
       </c>
       <c r="E77">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12447,7 +12447,7 @@
         <v>27</v>
       </c>
       <c r="E111">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14609,7 +14609,7 @@
         <v>27</v>
       </c>
       <c r="E205">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15483,7 +15483,7 @@
         <v>27</v>
       </c>
       <c r="E243">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F243" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16679,7 +16679,7 @@
         <v>27</v>
       </c>
       <c r="E295">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F295" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17944,7 +17944,7 @@
         <v>27</v>
       </c>
       <c r="E350">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F350" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>

--- a/all-test-reports/appium/appium_test_report.xlsx
+++ b/all-test-reports/appium/appium_test_report.xlsx
@@ -42,7 +42,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:43:46 am</t>
+    <t>28/7/2026, 11:57:31 am</t>
   </si>
   <si>
     <t>Total Duration</t>
@@ -1847,7 +1847,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="11">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>28</v>
@@ -1870,7 +1870,7 @@
         <v>27</v>
       </c>
       <c r="E3" s="11">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>28</v>
@@ -1893,7 +1893,7 @@
         <v>27</v>
       </c>
       <c r="E4" s="11">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>28</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="11">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>28</v>
@@ -1939,7 +1939,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="11">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>28</v>
@@ -1962,7 +1962,7 @@
         <v>27</v>
       </c>
       <c r="E7" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>28</v>
@@ -1985,7 +1985,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="11">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>28</v>
@@ -2008,7 +2008,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="11">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>28</v>
@@ -2031,7 +2031,7 @@
         <v>27</v>
       </c>
       <c r="E10" s="11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>28</v>
@@ -2054,7 +2054,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>28</v>
@@ -2077,7 +2077,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="11">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>28</v>
@@ -2100,7 +2100,7 @@
         <v>27</v>
       </c>
       <c r="E13" s="11">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>28</v>
@@ -2123,7 +2123,7 @@
         <v>27</v>
       </c>
       <c r="E14" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>28</v>
@@ -2169,7 +2169,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>28</v>
@@ -2215,7 +2215,7 @@
         <v>27</v>
       </c>
       <c r="E18" s="11">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>28</v>
@@ -2238,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="E19" s="11">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>28</v>
@@ -2261,7 +2261,7 @@
         <v>27</v>
       </c>
       <c r="E20" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>28</v>
@@ -2284,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="E21" s="11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>28</v>
@@ -2307,7 +2307,7 @@
         <v>27</v>
       </c>
       <c r="E22" s="11">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>28</v>
@@ -2330,7 +2330,7 @@
         <v>27</v>
       </c>
       <c r="E23" s="11">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>28</v>
@@ -2353,7 +2353,7 @@
         <v>27</v>
       </c>
       <c r="E24" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>28</v>
@@ -2376,7 +2376,7 @@
         <v>27</v>
       </c>
       <c r="E25" s="11">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>28</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="E26" s="11">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>28</v>
@@ -2422,7 +2422,7 @@
         <v>27</v>
       </c>
       <c r="E27" s="11">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>28</v>
@@ -2445,7 +2445,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="11">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>28</v>
@@ -2468,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="E29" s="11">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>28</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="E30" s="11">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>28</v>
@@ -2514,7 +2514,7 @@
         <v>27</v>
       </c>
       <c r="E31" s="11">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>28</v>
@@ -2537,7 +2537,7 @@
         <v>27</v>
       </c>
       <c r="E32" s="11">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>28</v>
@@ -2560,7 +2560,7 @@
         <v>27</v>
       </c>
       <c r="E33" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>28</v>
@@ -2583,7 +2583,7 @@
         <v>27</v>
       </c>
       <c r="E34" s="11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>28</v>
@@ -2606,7 +2606,7 @@
         <v>27</v>
       </c>
       <c r="E35" s="11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>28</v>
@@ -2629,7 +2629,7 @@
         <v>27</v>
       </c>
       <c r="E36" s="11">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>28</v>
@@ -2652,7 +2652,7 @@
         <v>27</v>
       </c>
       <c r="E37" s="11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>28</v>
@@ -2675,7 +2675,7 @@
         <v>27</v>
       </c>
       <c r="E38" s="11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>28</v>
@@ -2698,7 +2698,7 @@
         <v>27</v>
       </c>
       <c r="E39" s="11">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>28</v>
@@ -2721,7 +2721,7 @@
         <v>27</v>
       </c>
       <c r="E40" s="11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>28</v>
@@ -2744,7 +2744,7 @@
         <v>27</v>
       </c>
       <c r="E41" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="11">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>28</v>
@@ -2790,7 +2790,7 @@
         <v>27</v>
       </c>
       <c r="E43" s="11">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>28</v>
@@ -2813,7 +2813,7 @@
         <v>27</v>
       </c>
       <c r="E44" s="11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>28</v>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
       <c r="E45" s="11">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>28</v>
@@ -2859,7 +2859,7 @@
         <v>27</v>
       </c>
       <c r="E46" s="11">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>28</v>
@@ -2882,7 +2882,7 @@
         <v>27</v>
       </c>
       <c r="E47" s="11">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>28</v>
@@ -2905,7 +2905,7 @@
         <v>27</v>
       </c>
       <c r="E48" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>28</v>
@@ -2928,7 +2928,7 @@
         <v>27</v>
       </c>
       <c r="E49" s="11">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>28</v>
@@ -2951,7 +2951,7 @@
         <v>27</v>
       </c>
       <c r="E50" s="11">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>28</v>
@@ -2974,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="E51" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>28</v>
@@ -2997,7 +2997,7 @@
         <v>27</v>
       </c>
       <c r="E52" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>28</v>
@@ -3020,7 +3020,7 @@
         <v>27</v>
       </c>
       <c r="E53" s="11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>28</v>
@@ -3043,7 +3043,7 @@
         <v>27</v>
       </c>
       <c r="E54" s="11">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>28</v>
@@ -3066,7 +3066,7 @@
         <v>27</v>
       </c>
       <c r="E55" s="11">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>28</v>
@@ -3089,7 +3089,7 @@
         <v>27</v>
       </c>
       <c r="E56" s="11">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>28</v>
@@ -3112,7 +3112,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="11">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>28</v>
@@ -3135,7 +3135,7 @@
         <v>27</v>
       </c>
       <c r="E58" s="11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>28</v>
@@ -3158,7 +3158,7 @@
         <v>27</v>
       </c>
       <c r="E59" s="11">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>28</v>
@@ -3181,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E60" s="11">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>28</v>
@@ -3204,7 +3204,7 @@
         <v>27</v>
       </c>
       <c r="E61" s="11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>28</v>
@@ -3227,7 +3227,7 @@
         <v>27</v>
       </c>
       <c r="E62" s="11">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>28</v>
@@ -3250,7 +3250,7 @@
         <v>27</v>
       </c>
       <c r="E63" s="11">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>28</v>
@@ -3273,7 +3273,7 @@
         <v>27</v>
       </c>
       <c r="E64" s="11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>28</v>
@@ -3296,7 +3296,7 @@
         <v>27</v>
       </c>
       <c r="E65" s="11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>28</v>
@@ -3319,7 +3319,7 @@
         <v>27</v>
       </c>
       <c r="E66" s="11">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>28</v>
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="E67" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>28</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="E68" s="11">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="E69" s="11">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>28</v>
@@ -3411,7 +3411,7 @@
         <v>27</v>
       </c>
       <c r="E70" s="11">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>28</v>
@@ -3434,7 +3434,7 @@
         <v>27</v>
       </c>
       <c r="E71" s="11">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>28</v>
@@ -3457,7 +3457,7 @@
         <v>27</v>
       </c>
       <c r="E72" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>28</v>
@@ -3480,7 +3480,7 @@
         <v>27</v>
       </c>
       <c r="E73" s="11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>28</v>
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="11">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>28</v>
@@ -3526,7 +3526,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="11">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>28</v>
@@ -3595,7 +3595,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="11">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>28</v>
@@ -3618,7 +3618,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>28</v>
@@ -3641,7 +3641,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="11">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>28</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="11">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>28</v>
@@ -3687,7 +3687,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>28</v>
@@ -3710,7 +3710,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="11">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>28</v>
@@ -3733,7 +3733,7 @@
         <v>27</v>
       </c>
       <c r="E84" s="11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>28</v>
@@ -3756,7 +3756,7 @@
         <v>27</v>
       </c>
       <c r="E85" s="11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>28</v>
@@ -3779,7 +3779,7 @@
         <v>27</v>
       </c>
       <c r="E86" s="11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>28</v>
@@ -3802,7 +3802,7 @@
         <v>27</v>
       </c>
       <c r="E87" s="11">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>28</v>
@@ -3825,7 +3825,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="11">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="11">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>28</v>
@@ -3871,7 +3871,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="11">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>28</v>
@@ -3894,7 +3894,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="11">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>28</v>
@@ -3917,7 +3917,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="11">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>28</v>
@@ -3940,7 +3940,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="11">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>28</v>
@@ -3963,7 +3963,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="11">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="11">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>28</v>
@@ -4009,7 +4009,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="11">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>28</v>
@@ -4032,7 +4032,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>28</v>
@@ -4055,7 +4055,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="11">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>28</v>
@@ -4078,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>28</v>
@@ -4101,7 +4101,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>28</v>
@@ -4124,7 +4124,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="11">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>28</v>
@@ -4147,7 +4147,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="11">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>28</v>
@@ -4170,7 +4170,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="11">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>28</v>
@@ -4193,7 +4193,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="11">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>28</v>
@@ -4216,7 +4216,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="11">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>28</v>
@@ -4239,7 +4239,7 @@
         <v>27</v>
       </c>
       <c r="E106" s="11">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>28</v>
@@ -4262,7 +4262,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="11">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>28</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="11">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>28</v>
@@ -4308,7 +4308,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="11">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>28</v>
@@ -4331,7 +4331,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="11">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>28</v>
@@ -4377,7 +4377,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="11">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>28</v>
@@ -4400,7 +4400,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="11">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>28</v>
@@ -4423,7 +4423,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>28</v>
@@ -4446,7 +4446,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="11">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>28</v>
@@ -4469,7 +4469,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>28</v>
@@ -4492,7 +4492,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>28</v>
@@ -4538,7 +4538,7 @@
         <v>27</v>
       </c>
       <c r="E119" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>28</v>
@@ -4561,7 +4561,7 @@
         <v>27</v>
       </c>
       <c r="E120" s="11">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="E121" s="11">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>28</v>
@@ -4607,7 +4607,7 @@
         <v>27</v>
       </c>
       <c r="E122" s="11">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>28</v>
@@ -4630,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="E123" s="11">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>28</v>
@@ -4653,7 +4653,7 @@
         <v>27</v>
       </c>
       <c r="E124" s="11">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>28</v>
@@ -4676,7 +4676,7 @@
         <v>27</v>
       </c>
       <c r="E125" s="11">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>28</v>
@@ -4699,7 +4699,7 @@
         <v>27</v>
       </c>
       <c r="E126" s="11">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>28</v>
@@ -4722,7 +4722,7 @@
         <v>27</v>
       </c>
       <c r="E127" s="11">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>28</v>
@@ -4745,7 +4745,7 @@
         <v>27</v>
       </c>
       <c r="E128" s="11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>28</v>
@@ -4768,7 +4768,7 @@
         <v>27</v>
       </c>
       <c r="E129" s="11">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>28</v>
@@ -4791,7 +4791,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="11">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>28</v>
@@ -4814,7 +4814,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="11">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>28</v>
@@ -4837,7 +4837,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>28</v>
@@ -4860,7 +4860,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="11">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>28</v>
@@ -4883,7 +4883,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="11">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>28</v>
@@ -4906,7 +4906,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>28</v>
@@ -4929,7 +4929,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="11">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>28</v>
@@ -4952,7 +4952,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>28</v>
@@ -4975,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>28</v>
@@ -4998,7 +4998,7 @@
         <v>27</v>
       </c>
       <c r="E139" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>28</v>
@@ -5021,7 +5021,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>28</v>
@@ -5044,7 +5044,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>28</v>
@@ -5067,7 +5067,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="11">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>28</v>
@@ -5090,7 +5090,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="11">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>28</v>
@@ -5113,7 +5113,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>28</v>
@@ -5136,7 +5136,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="11">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>28</v>
@@ -5159,7 +5159,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="11">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>28</v>
@@ -5205,7 +5205,7 @@
         <v>27</v>
       </c>
       <c r="E148" s="11">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>28</v>
@@ -5228,7 +5228,7 @@
         <v>27</v>
       </c>
       <c r="E149" s="11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>28</v>
@@ -5251,7 +5251,7 @@
         <v>27</v>
       </c>
       <c r="E150" s="11">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>28</v>
@@ -5274,7 +5274,7 @@
         <v>27</v>
       </c>
       <c r="E151" s="11">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="E152" s="11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>28</v>
@@ -5320,7 +5320,7 @@
         <v>27</v>
       </c>
       <c r="E153" s="11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>28</v>
@@ -5343,7 +5343,7 @@
         <v>27</v>
       </c>
       <c r="E154" s="11">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>28</v>
@@ -5366,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="E155" s="11">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>28</v>
@@ -5389,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="E156" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>28</v>
@@ -5412,7 +5412,7 @@
         <v>27</v>
       </c>
       <c r="E157" s="11">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>28</v>
@@ -5435,7 +5435,7 @@
         <v>27</v>
       </c>
       <c r="E158" s="11">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>28</v>
@@ -5458,7 +5458,7 @@
         <v>27</v>
       </c>
       <c r="E159" s="11">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>28</v>
@@ -5481,7 +5481,7 @@
         <v>27</v>
       </c>
       <c r="E160" s="11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>28</v>
@@ -5504,7 +5504,7 @@
         <v>27</v>
       </c>
       <c r="E161" s="11">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>28</v>
@@ -5527,7 +5527,7 @@
         <v>27</v>
       </c>
       <c r="E162" s="11">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>28</v>
@@ -5550,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="E163" s="11">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>28</v>
@@ -5573,7 +5573,7 @@
         <v>27</v>
       </c>
       <c r="E164" s="11">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F164" s="9" t="s">
         <v>28</v>
@@ -5596,7 +5596,7 @@
         <v>27</v>
       </c>
       <c r="E165" s="11">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>28</v>
@@ -5619,7 +5619,7 @@
         <v>27</v>
       </c>
       <c r="E166" s="11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F166" s="9" t="s">
         <v>28</v>
@@ -5642,7 +5642,7 @@
         <v>27</v>
       </c>
       <c r="E167" s="11">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>28</v>
@@ -5665,7 +5665,7 @@
         <v>27</v>
       </c>
       <c r="E168" s="11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F168" s="9" t="s">
         <v>28</v>
@@ -5688,7 +5688,7 @@
         <v>27</v>
       </c>
       <c r="E169" s="11">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>28</v>
@@ -5711,7 +5711,7 @@
         <v>27</v>
       </c>
       <c r="E170" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F170" s="9" t="s">
         <v>28</v>
@@ -5734,7 +5734,7 @@
         <v>27</v>
       </c>
       <c r="E171" s="11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>28</v>
@@ -5757,7 +5757,7 @@
         <v>27</v>
       </c>
       <c r="E172" s="11">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F172" s="9" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="E173" s="11">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>28</v>
@@ -5803,7 +5803,7 @@
         <v>27</v>
       </c>
       <c r="E174" s="11">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F174" s="9" t="s">
         <v>28</v>
@@ -5826,7 +5826,7 @@
         <v>27</v>
       </c>
       <c r="E175" s="11">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>28</v>
@@ -5849,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="E176" s="11">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F176" s="9" t="s">
         <v>28</v>
@@ -5872,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E177" s="11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>28</v>
@@ -5895,7 +5895,7 @@
         <v>27</v>
       </c>
       <c r="E178" s="11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F178" s="9" t="s">
         <v>28</v>
@@ -5918,7 +5918,7 @@
         <v>27</v>
       </c>
       <c r="E179" s="11">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>28</v>
@@ -5941,7 +5941,7 @@
         <v>27</v>
       </c>
       <c r="E180" s="11">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F180" s="9" t="s">
         <v>28</v>
@@ -5964,7 +5964,7 @@
         <v>27</v>
       </c>
       <c r="E181" s="11">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>28</v>
@@ -5987,7 +5987,7 @@
         <v>27</v>
       </c>
       <c r="E182" s="11">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F182" s="9" t="s">
         <v>28</v>
@@ -6010,7 +6010,7 @@
         <v>27</v>
       </c>
       <c r="E183" s="11">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>28</v>
@@ -6033,7 +6033,7 @@
         <v>27</v>
       </c>
       <c r="E184" s="11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F184" s="9" t="s">
         <v>28</v>
@@ -6056,7 +6056,7 @@
         <v>27</v>
       </c>
       <c r="E185" s="11">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>28</v>
@@ -6079,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="E186" s="11">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F186" s="9" t="s">
         <v>28</v>
@@ -6102,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="E187" s="11">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>28</v>
@@ -6125,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="E188" s="11">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F188" s="9" t="s">
         <v>28</v>
@@ -6148,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="E189" s="11">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>28</v>
@@ -6171,7 +6171,7 @@
         <v>27</v>
       </c>
       <c r="E190" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F190" s="9" t="s">
         <v>28</v>
@@ -6194,7 +6194,7 @@
         <v>27</v>
       </c>
       <c r="E191" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>28</v>
@@ -6217,7 +6217,7 @@
         <v>27</v>
       </c>
       <c r="E192" s="11">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F192" s="9" t="s">
         <v>28</v>
@@ -6240,7 +6240,7 @@
         <v>27</v>
       </c>
       <c r="E193" s="11">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>28</v>
@@ -6263,7 +6263,7 @@
         <v>27</v>
       </c>
       <c r="E194" s="11">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F194" s="9" t="s">
         <v>28</v>
@@ -6286,7 +6286,7 @@
         <v>27</v>
       </c>
       <c r="E195" s="11">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>28</v>
@@ -6309,7 +6309,7 @@
         <v>27</v>
       </c>
       <c r="E196" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F196" s="9" t="s">
         <v>28</v>
@@ -6332,7 +6332,7 @@
         <v>27</v>
       </c>
       <c r="E197" s="11">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>28</v>
@@ -6355,7 +6355,7 @@
         <v>27</v>
       </c>
       <c r="E198" s="11">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F198" s="9" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="E199" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>28</v>
@@ -6401,7 +6401,7 @@
         <v>27</v>
       </c>
       <c r="E200" s="11">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F200" s="9" t="s">
         <v>28</v>
@@ -6424,7 +6424,7 @@
         <v>27</v>
       </c>
       <c r="E201" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>27</v>
       </c>
       <c r="E202" s="11">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F202" s="9" t="s">
         <v>28</v>
@@ -6470,7 +6470,7 @@
         <v>27</v>
       </c>
       <c r="E203" s="11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>28</v>
@@ -6493,7 +6493,7 @@
         <v>27</v>
       </c>
       <c r="E204" s="11">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F204" s="9" t="s">
         <v>28</v>
@@ -6539,7 +6539,7 @@
         <v>27</v>
       </c>
       <c r="E206" s="11">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F206" s="9" t="s">
         <v>28</v>
@@ -6562,7 +6562,7 @@
         <v>27</v>
       </c>
       <c r="E207" s="11">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>28</v>
@@ -6585,7 +6585,7 @@
         <v>27</v>
       </c>
       <c r="E208" s="11">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F208" s="9" t="s">
         <v>28</v>
@@ -6608,7 +6608,7 @@
         <v>27</v>
       </c>
       <c r="E209" s="11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F209" s="9" t="s">
         <v>28</v>
@@ -6631,7 +6631,7 @@
         <v>27</v>
       </c>
       <c r="E210" s="11">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F210" s="9" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>27</v>
       </c>
       <c r="E211" s="11">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F211" s="9" t="s">
         <v>28</v>
@@ -6677,7 +6677,7 @@
         <v>27</v>
       </c>
       <c r="E212" s="11">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F212" s="9" t="s">
         <v>28</v>
@@ -6700,7 +6700,7 @@
         <v>27</v>
       </c>
       <c r="E213" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F213" s="9" t="s">
         <v>28</v>
@@ -6723,7 +6723,7 @@
         <v>27</v>
       </c>
       <c r="E214" s="11">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F214" s="9" t="s">
         <v>28</v>
@@ -6746,7 +6746,7 @@
         <v>27</v>
       </c>
       <c r="E215" s="11">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F215" s="9" t="s">
         <v>28</v>
@@ -6769,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="E216" s="11">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F216" s="9" t="s">
         <v>28</v>
@@ -6792,7 +6792,7 @@
         <v>27</v>
       </c>
       <c r="E217" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F217" s="9" t="s">
         <v>28</v>
@@ -6815,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="E218" s="11">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F218" s="9" t="s">
         <v>28</v>
@@ -6838,7 +6838,7 @@
         <v>27</v>
       </c>
       <c r="E219" s="11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F219" s="9" t="s">
         <v>28</v>
@@ -6861,7 +6861,7 @@
         <v>27</v>
       </c>
       <c r="E220" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F220" s="9" t="s">
         <v>28</v>
@@ -6884,7 +6884,7 @@
         <v>27</v>
       </c>
       <c r="E221" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F221" s="9" t="s">
         <v>28</v>
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="E222" s="11">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F222" s="9" t="s">
         <v>28</v>
@@ -6930,7 +6930,7 @@
         <v>27</v>
       </c>
       <c r="E223" s="11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F223" s="9" t="s">
         <v>28</v>
@@ -6953,7 +6953,7 @@
         <v>27</v>
       </c>
       <c r="E224" s="11">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F224" s="9" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="E225" s="11">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F225" s="9" t="s">
         <v>28</v>
@@ -6999,7 +6999,7 @@
         <v>27</v>
       </c>
       <c r="E226" s="11">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F226" s="9" t="s">
         <v>28</v>
@@ -7022,7 +7022,7 @@
         <v>27</v>
       </c>
       <c r="E227" s="11">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F227" s="9" t="s">
         <v>28</v>
@@ -7045,7 +7045,7 @@
         <v>27</v>
       </c>
       <c r="E228" s="11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F228" s="9" t="s">
         <v>28</v>
@@ -7068,7 +7068,7 @@
         <v>27</v>
       </c>
       <c r="E229" s="11">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F229" s="9" t="s">
         <v>28</v>
@@ -7091,7 +7091,7 @@
         <v>27</v>
       </c>
       <c r="E230" s="11">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F230" s="9" t="s">
         <v>28</v>
@@ -7114,7 +7114,7 @@
         <v>27</v>
       </c>
       <c r="E231" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F231" s="9" t="s">
         <v>28</v>
@@ -7137,7 +7137,7 @@
         <v>27</v>
       </c>
       <c r="E232" s="11">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F232" s="9" t="s">
         <v>28</v>
@@ -7160,7 +7160,7 @@
         <v>27</v>
       </c>
       <c r="E233" s="11">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F233" s="9" t="s">
         <v>28</v>
@@ -7183,7 +7183,7 @@
         <v>27</v>
       </c>
       <c r="E234" s="11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F234" s="9" t="s">
         <v>28</v>
@@ -7206,7 +7206,7 @@
         <v>27</v>
       </c>
       <c r="E235" s="11">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F235" s="9" t="s">
         <v>28</v>
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="E236" s="11">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F236" s="9" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>27</v>
       </c>
       <c r="E237" s="11">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F237" s="9" t="s">
         <v>28</v>
@@ -7275,7 +7275,7 @@
         <v>27</v>
       </c>
       <c r="E238" s="11">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F238" s="9" t="s">
         <v>28</v>
@@ -7298,7 +7298,7 @@
         <v>27</v>
       </c>
       <c r="E239" s="11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F239" s="9" t="s">
         <v>28</v>
@@ -7321,7 +7321,7 @@
         <v>27</v>
       </c>
       <c r="E240" s="11">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F240" s="9" t="s">
         <v>28</v>
@@ -7344,7 +7344,7 @@
         <v>27</v>
       </c>
       <c r="E241" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F241" s="9" t="s">
         <v>28</v>
@@ -7367,7 +7367,7 @@
         <v>27</v>
       </c>
       <c r="E242" s="11">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F242" s="9" t="s">
         <v>28</v>
@@ -7413,7 +7413,7 @@
         <v>27</v>
       </c>
       <c r="E244" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F244" s="9" t="s">
         <v>28</v>
@@ -7436,7 +7436,7 @@
         <v>27</v>
       </c>
       <c r="E245" s="11">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F245" s="9" t="s">
         <v>28</v>
@@ -7459,7 +7459,7 @@
         <v>27</v>
       </c>
       <c r="E246" s="11">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F246" s="9" t="s">
         <v>28</v>
@@ -7482,7 +7482,7 @@
         <v>27</v>
       </c>
       <c r="E247" s="11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F247" s="9" t="s">
         <v>28</v>
@@ -7505,7 +7505,7 @@
         <v>27</v>
       </c>
       <c r="E248" s="11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F248" s="9" t="s">
         <v>28</v>
@@ -7528,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="E249" s="11">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F249" s="9" t="s">
         <v>28</v>
@@ -7551,7 +7551,7 @@
         <v>27</v>
       </c>
       <c r="E250" s="11">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F250" s="9" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="11">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F251" s="9" t="s">
         <v>28</v>
@@ -7597,7 +7597,7 @@
         <v>27</v>
       </c>
       <c r="E252" s="11">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F252" s="9" t="s">
         <v>28</v>
@@ -7620,7 +7620,7 @@
         <v>27</v>
       </c>
       <c r="E253" s="11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F253" s="9" t="s">
         <v>28</v>
@@ -7643,7 +7643,7 @@
         <v>27</v>
       </c>
       <c r="E254" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F254" s="9" t="s">
         <v>28</v>
@@ -7666,7 +7666,7 @@
         <v>27</v>
       </c>
       <c r="E255" s="11">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F255" s="9" t="s">
         <v>28</v>
@@ -7689,7 +7689,7 @@
         <v>27</v>
       </c>
       <c r="E256" s="11">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F256" s="9" t="s">
         <v>28</v>
@@ -7712,7 +7712,7 @@
         <v>27</v>
       </c>
       <c r="E257" s="11">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F257" s="9" t="s">
         <v>28</v>
@@ -7735,7 +7735,7 @@
         <v>27</v>
       </c>
       <c r="E258" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F258" s="9" t="s">
         <v>28</v>
@@ -7758,7 +7758,7 @@
         <v>27</v>
       </c>
       <c r="E259" s="11">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F259" s="9" t="s">
         <v>28</v>
@@ -7781,7 +7781,7 @@
         <v>27</v>
       </c>
       <c r="E260" s="11">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F260" s="9" t="s">
         <v>28</v>
@@ -7804,7 +7804,7 @@
         <v>27</v>
       </c>
       <c r="E261" s="11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F261" s="9" t="s">
         <v>28</v>
@@ -7827,7 +7827,7 @@
         <v>27</v>
       </c>
       <c r="E262" s="11">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F262" s="9" t="s">
         <v>28</v>
@@ -7850,7 +7850,7 @@
         <v>27</v>
       </c>
       <c r="E263" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F263" s="9" t="s">
         <v>28</v>
@@ -7873,7 +7873,7 @@
         <v>27</v>
       </c>
       <c r="E264" s="11">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F264" s="9" t="s">
         <v>28</v>
@@ -7896,7 +7896,7 @@
         <v>27</v>
       </c>
       <c r="E265" s="11">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F265" s="9" t="s">
         <v>28</v>
@@ -7919,7 +7919,7 @@
         <v>27</v>
       </c>
       <c r="E266" s="11">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F266" s="9" t="s">
         <v>28</v>
@@ -7942,7 +7942,7 @@
         <v>27</v>
       </c>
       <c r="E267" s="11">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F267" s="9" t="s">
         <v>28</v>
@@ -7965,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="E268" s="11">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F268" s="9" t="s">
         <v>28</v>
@@ -7988,7 +7988,7 @@
         <v>27</v>
       </c>
       <c r="E269" s="11">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F269" s="9" t="s">
         <v>28</v>
@@ -8011,7 +8011,7 @@
         <v>27</v>
       </c>
       <c r="E270" s="11">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F270" s="9" t="s">
         <v>28</v>
@@ -8034,7 +8034,7 @@
         <v>27</v>
       </c>
       <c r="E271" s="11">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F271" s="9" t="s">
         <v>28</v>
@@ -8057,7 +8057,7 @@
         <v>27</v>
       </c>
       <c r="E272" s="11">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F272" s="9" t="s">
         <v>28</v>
@@ -8080,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="E273" s="11">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F273" s="9" t="s">
         <v>28</v>
@@ -8103,7 +8103,7 @@
         <v>27</v>
       </c>
       <c r="E274" s="11">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F274" s="9" t="s">
         <v>28</v>
@@ -8126,7 +8126,7 @@
         <v>27</v>
       </c>
       <c r="E275" s="11">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F275" s="9" t="s">
         <v>28</v>
@@ -8149,7 +8149,7 @@
         <v>27</v>
       </c>
       <c r="E276" s="11">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F276" s="9" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="E277" s="11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F277" s="9" t="s">
         <v>28</v>
@@ -8195,7 +8195,7 @@
         <v>27</v>
       </c>
       <c r="E278" s="11">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F278" s="9" t="s">
         <v>28</v>
@@ -8218,7 +8218,7 @@
         <v>27</v>
       </c>
       <c r="E279" s="11">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F279" s="9" t="s">
         <v>28</v>
@@ -8241,7 +8241,7 @@
         <v>27</v>
       </c>
       <c r="E280" s="11">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F280" s="9" t="s">
         <v>28</v>
@@ -8264,7 +8264,7 @@
         <v>27</v>
       </c>
       <c r="E281" s="11">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F281" s="9" t="s">
         <v>28</v>
@@ -8287,7 +8287,7 @@
         <v>27</v>
       </c>
       <c r="E282" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F282" s="9" t="s">
         <v>28</v>
@@ -8310,7 +8310,7 @@
         <v>27</v>
       </c>
       <c r="E283" s="11">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F283" s="9" t="s">
         <v>28</v>
@@ -8333,7 +8333,7 @@
         <v>27</v>
       </c>
       <c r="E284" s="11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F284" s="9" t="s">
         <v>28</v>
@@ -8356,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="E285" s="11">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F285" s="9" t="s">
         <v>28</v>
@@ -8379,7 +8379,7 @@
         <v>27</v>
       </c>
       <c r="E286" s="11">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F286" s="9" t="s">
         <v>28</v>
@@ -8402,7 +8402,7 @@
         <v>27</v>
       </c>
       <c r="E287" s="11">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F287" s="9" t="s">
         <v>28</v>
@@ -8425,7 +8425,7 @@
         <v>27</v>
       </c>
       <c r="E288" s="11">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F288" s="9" t="s">
         <v>28</v>
@@ -8448,7 +8448,7 @@
         <v>27</v>
       </c>
       <c r="E289" s="11">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F289" s="9" t="s">
         <v>28</v>
@@ -8471,7 +8471,7 @@
         <v>27</v>
       </c>
       <c r="E290" s="11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F290" s="9" t="s">
         <v>28</v>
@@ -8494,7 +8494,7 @@
         <v>27</v>
       </c>
       <c r="E291" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F291" s="9" t="s">
         <v>28</v>
@@ -8517,7 +8517,7 @@
         <v>27</v>
       </c>
       <c r="E292" s="11">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F292" s="9" t="s">
         <v>28</v>
@@ -8540,7 +8540,7 @@
         <v>27</v>
       </c>
       <c r="E293" s="11">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F293" s="9" t="s">
         <v>28</v>
@@ -8563,7 +8563,7 @@
         <v>27</v>
       </c>
       <c r="E294" s="11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F294" s="9" t="s">
         <v>28</v>
@@ -8609,7 +8609,7 @@
         <v>27</v>
       </c>
       <c r="E296" s="11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F296" s="9" t="s">
         <v>28</v>
@@ -8632,7 +8632,7 @@
         <v>27</v>
       </c>
       <c r="E297" s="11">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F297" s="9" t="s">
         <v>28</v>
@@ -8655,7 +8655,7 @@
         <v>27</v>
       </c>
       <c r="E298" s="11">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F298" s="9" t="s">
         <v>28</v>
@@ -8678,7 +8678,7 @@
         <v>27</v>
       </c>
       <c r="E299" s="11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F299" s="9" t="s">
         <v>28</v>
@@ -8701,7 +8701,7 @@
         <v>27</v>
       </c>
       <c r="E300" s="11">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F300" s="9" t="s">
         <v>28</v>
@@ -8724,7 +8724,7 @@
         <v>27</v>
       </c>
       <c r="E301" s="11">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F301" s="9" t="s">
         <v>28</v>
@@ -8747,7 +8747,7 @@
         <v>27</v>
       </c>
       <c r="E302" s="11">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F302" s="9" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="E303" s="11">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F303" s="9" t="s">
         <v>28</v>
@@ -8793,7 +8793,7 @@
         <v>27</v>
       </c>
       <c r="E304" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F304" s="9" t="s">
         <v>28</v>
@@ -8816,7 +8816,7 @@
         <v>27</v>
       </c>
       <c r="E305" s="11">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F305" s="9" t="s">
         <v>28</v>
@@ -8839,7 +8839,7 @@
         <v>27</v>
       </c>
       <c r="E306" s="11">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F306" s="9" t="s">
         <v>28</v>
@@ -8862,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="E307" s="11">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F307" s="9" t="s">
         <v>28</v>
@@ -8885,7 +8885,7 @@
         <v>27</v>
       </c>
       <c r="E308" s="11">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F308" s="9" t="s">
         <v>28</v>
@@ -8908,7 +8908,7 @@
         <v>27</v>
       </c>
       <c r="E309" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F309" s="9" t="s">
         <v>28</v>
@@ -8931,7 +8931,7 @@
         <v>27</v>
       </c>
       <c r="E310" s="11">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F310" s="9" t="s">
         <v>28</v>
@@ -8954,7 +8954,7 @@
         <v>27</v>
       </c>
       <c r="E311" s="11">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F311" s="9" t="s">
         <v>28</v>
@@ -8977,7 +8977,7 @@
         <v>27</v>
       </c>
       <c r="E312" s="11">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F312" s="9" t="s">
         <v>28</v>
@@ -9000,7 +9000,7 @@
         <v>27</v>
       </c>
       <c r="E313" s="11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F313" s="9" t="s">
         <v>28</v>
@@ -9023,7 +9023,7 @@
         <v>27</v>
       </c>
       <c r="E314" s="11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F314" s="9" t="s">
         <v>28</v>
@@ -9046,7 +9046,7 @@
         <v>27</v>
       </c>
       <c r="E315" s="11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F315" s="9" t="s">
         <v>28</v>
@@ -9069,7 +9069,7 @@
         <v>27</v>
       </c>
       <c r="E316" s="11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F316" s="9" t="s">
         <v>28</v>
@@ -9092,7 +9092,7 @@
         <v>27</v>
       </c>
       <c r="E317" s="11">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F317" s="9" t="s">
         <v>28</v>
@@ -9115,7 +9115,7 @@
         <v>27</v>
       </c>
       <c r="E318" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F318" s="9" t="s">
         <v>28</v>
@@ -9138,7 +9138,7 @@
         <v>27</v>
       </c>
       <c r="E319" s="11">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F319" s="9" t="s">
         <v>28</v>
@@ -9161,7 +9161,7 @@
         <v>27</v>
       </c>
       <c r="E320" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F320" s="9" t="s">
         <v>28</v>
@@ -9184,7 +9184,7 @@
         <v>27</v>
       </c>
       <c r="E321" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F321" s="9" t="s">
         <v>28</v>
@@ -9207,7 +9207,7 @@
         <v>27</v>
       </c>
       <c r="E322" s="11">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F322" s="9" t="s">
         <v>28</v>
@@ -9230,7 +9230,7 @@
         <v>27</v>
       </c>
       <c r="E323" s="11">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F323" s="9" t="s">
         <v>28</v>
@@ -9253,7 +9253,7 @@
         <v>27</v>
       </c>
       <c r="E324" s="11">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F324" s="9" t="s">
         <v>28</v>
@@ -9276,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E325" s="11">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F325" s="9" t="s">
         <v>28</v>
@@ -9299,7 +9299,7 @@
         <v>27</v>
       </c>
       <c r="E326" s="11">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F326" s="9" t="s">
         <v>28</v>
@@ -9322,7 +9322,7 @@
         <v>27</v>
       </c>
       <c r="E327" s="11">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F327" s="9" t="s">
         <v>28</v>
@@ -9345,7 +9345,7 @@
         <v>27</v>
       </c>
       <c r="E328" s="11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F328" s="9" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="E329" s="11">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F329" s="9" t="s">
         <v>28</v>
@@ -9391,7 +9391,7 @@
         <v>27</v>
       </c>
       <c r="E330" s="11">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F330" s="9" t="s">
         <v>28</v>
@@ -9414,7 +9414,7 @@
         <v>27</v>
       </c>
       <c r="E331" s="11">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F331" s="9" t="s">
         <v>28</v>
@@ -9437,7 +9437,7 @@
         <v>27</v>
       </c>
       <c r="E332" s="11">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F332" s="9" t="s">
         <v>28</v>
@@ -9460,7 +9460,7 @@
         <v>27</v>
       </c>
       <c r="E333" s="11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F333" s="9" t="s">
         <v>28</v>
@@ -9483,7 +9483,7 @@
         <v>27</v>
       </c>
       <c r="E334" s="11">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F334" s="9" t="s">
         <v>28</v>
@@ -9506,7 +9506,7 @@
         <v>27</v>
       </c>
       <c r="E335" s="11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F335" s="9" t="s">
         <v>28</v>
@@ -9529,7 +9529,7 @@
         <v>27</v>
       </c>
       <c r="E336" s="11">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F336" s="9" t="s">
         <v>28</v>
@@ -9552,7 +9552,7 @@
         <v>27</v>
       </c>
       <c r="E337" s="11">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F337" s="9" t="s">
         <v>28</v>
@@ -9575,7 +9575,7 @@
         <v>27</v>
       </c>
       <c r="E338" s="11">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F338" s="9" t="s">
         <v>28</v>
@@ -9598,7 +9598,7 @@
         <v>27</v>
       </c>
       <c r="E339" s="11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F339" s="9" t="s">
         <v>28</v>
@@ -9621,7 +9621,7 @@
         <v>27</v>
       </c>
       <c r="E340" s="11">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F340" s="9" t="s">
         <v>28</v>
@@ -9644,7 +9644,7 @@
         <v>27</v>
       </c>
       <c r="E341" s="11">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F341" s="9" t="s">
         <v>28</v>
@@ -9667,7 +9667,7 @@
         <v>27</v>
       </c>
       <c r="E342" s="11">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F342" s="9" t="s">
         <v>28</v>
@@ -9690,7 +9690,7 @@
         <v>27</v>
       </c>
       <c r="E343" s="11">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F343" s="9" t="s">
         <v>28</v>
@@ -9713,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="E344" s="11">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F344" s="9" t="s">
         <v>28</v>
@@ -9736,7 +9736,7 @@
         <v>27</v>
       </c>
       <c r="E345" s="11">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F345" s="9" t="s">
         <v>28</v>
@@ -9759,7 +9759,7 @@
         <v>27</v>
       </c>
       <c r="E346" s="11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F346" s="9" t="s">
         <v>28</v>
@@ -9782,7 +9782,7 @@
         <v>27</v>
       </c>
       <c r="E347" s="11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F347" s="9" t="s">
         <v>28</v>
@@ -9805,7 +9805,7 @@
         <v>27</v>
       </c>
       <c r="E348" s="11">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F348" s="9" t="s">
         <v>28</v>
@@ -9828,7 +9828,7 @@
         <v>27</v>
       </c>
       <c r="E349" s="11">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F349" s="9" t="s">
         <v>28</v>
@@ -9874,7 +9874,7 @@
         <v>27</v>
       </c>
       <c r="E351" s="11">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F351" s="9" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
         <v>28</v>
@@ -9963,7 +9963,7 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
@@ -9986,7 +9986,7 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -10009,7 +10009,7 @@
         <v>27</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>28</v>
@@ -10032,7 +10032,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
         <v>28</v>
@@ -10055,7 +10055,7 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>
@@ -10078,7 +10078,7 @@
         <v>27</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
@@ -10101,7 +10101,7 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
         <v>28</v>
@@ -10124,7 +10124,7 @@
         <v>27</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
         <v>28</v>
@@ -10147,7 +10147,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
         <v>28</v>
@@ -10170,7 +10170,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
         <v>28</v>
@@ -10193,7 +10193,7 @@
         <v>27</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
         <v>28</v>
@@ -10216,7 +10216,7 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>28</v>
@@ -10262,7 +10262,7 @@
         <v>27</v>
       </c>
       <c r="E16">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
         <v>28</v>
@@ -10308,7 +10308,7 @@
         <v>27</v>
       </c>
       <c r="E18">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
         <v>28</v>
@@ -10331,7 +10331,7 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
         <v>28</v>
@@ -10354,7 +10354,7 @@
         <v>27</v>
       </c>
       <c r="E20">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
         <v>28</v>
@@ -10377,7 +10377,7 @@
         <v>27</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
         <v>28</v>
@@ -10400,7 +10400,7 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
         <v>28</v>
@@ -10423,7 +10423,7 @@
         <v>27</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
         <v>28</v>
@@ -10446,7 +10446,7 @@
         <v>27</v>
       </c>
       <c r="E24">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" t="s">
         <v>28</v>
@@ -10469,7 +10469,7 @@
         <v>27</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
         <v>28</v>
@@ -10492,7 +10492,7 @@
         <v>27</v>
       </c>
       <c r="E26">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
         <v>28</v>
@@ -10515,7 +10515,7 @@
         <v>27</v>
       </c>
       <c r="E27">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
@@ -10561,7 +10561,7 @@
         <v>27</v>
       </c>
       <c r="E29">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
@@ -10584,7 +10584,7 @@
         <v>27</v>
       </c>
       <c r="E30">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
@@ -10607,7 +10607,7 @@
         <v>27</v>
       </c>
       <c r="E31">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
@@ -10630,7 +10630,7 @@
         <v>27</v>
       </c>
       <c r="E32">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -10653,7 +10653,7 @@
         <v>27</v>
       </c>
       <c r="E33">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -10676,7 +10676,7 @@
         <v>27</v>
       </c>
       <c r="E34">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -10699,7 +10699,7 @@
         <v>27</v>
       </c>
       <c r="E35">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -10722,7 +10722,7 @@
         <v>27</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -10745,7 +10745,7 @@
         <v>27</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -10768,7 +10768,7 @@
         <v>27</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -10791,7 +10791,7 @@
         <v>27</v>
       </c>
       <c r="E39">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -10814,7 +10814,7 @@
         <v>27</v>
       </c>
       <c r="E40">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -10837,7 +10837,7 @@
         <v>27</v>
       </c>
       <c r="E41">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -10860,7 +10860,7 @@
         <v>27</v>
       </c>
       <c r="E42">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -10883,7 +10883,7 @@
         <v>27</v>
       </c>
       <c r="E43">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -10906,7 +10906,7 @@
         <v>27</v>
       </c>
       <c r="E44">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
         <v>28</v>
@@ -10929,7 +10929,7 @@
         <v>27</v>
       </c>
       <c r="E45">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F45" t="s">
         <v>28</v>
@@ -10952,7 +10952,7 @@
         <v>27</v>
       </c>
       <c r="E46">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
         <v>28</v>
@@ -10975,7 +10975,7 @@
         <v>27</v>
       </c>
       <c r="E47">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
         <v>28</v>
@@ -10998,7 +10998,7 @@
         <v>27</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F48" t="s">
         <v>28</v>
@@ -11021,7 +11021,7 @@
         <v>27</v>
       </c>
       <c r="E49">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F49" t="s">
         <v>28</v>
@@ -11044,7 +11044,7 @@
         <v>27</v>
       </c>
       <c r="E50">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
         <v>28</v>
@@ -11067,7 +11067,7 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
         <v>28</v>
@@ -11090,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="E52">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F52" t="s">
         <v>28</v>
@@ -11113,7 +11113,7 @@
         <v>27</v>
       </c>
       <c r="E53">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="E54">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F54" t="s">
         <v>28</v>
@@ -11159,7 +11159,7 @@
         <v>27</v>
       </c>
       <c r="E55">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
         <v>28</v>
@@ -11182,7 +11182,7 @@
         <v>27</v>
       </c>
       <c r="E56">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
         <v>28</v>
@@ -11205,7 +11205,7 @@
         <v>27</v>
       </c>
       <c r="E57">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
@@ -11228,7 +11228,7 @@
         <v>27</v>
       </c>
       <c r="E58">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
         <v>28</v>
@@ -11251,7 +11251,7 @@
         <v>27</v>
       </c>
       <c r="E59">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
@@ -11274,7 +11274,7 @@
         <v>27</v>
       </c>
       <c r="E60">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
@@ -11297,7 +11297,7 @@
         <v>27</v>
       </c>
       <c r="E61">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
@@ -11320,7 +11320,7 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
@@ -11343,7 +11343,7 @@
         <v>27</v>
       </c>
       <c r="E63">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
@@ -11366,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E64">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
@@ -11389,7 +11389,7 @@
         <v>27</v>
       </c>
       <c r="E65">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
@@ -11412,7 +11412,7 @@
         <v>27</v>
       </c>
       <c r="E66">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
@@ -11435,7 +11435,7 @@
         <v>27</v>
       </c>
       <c r="E67">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="E68">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
@@ -11481,7 +11481,7 @@
         <v>27</v>
       </c>
       <c r="E69">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
@@ -11504,7 +11504,7 @@
         <v>27</v>
       </c>
       <c r="E70">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
@@ -11527,7 +11527,7 @@
         <v>27</v>
       </c>
       <c r="E71">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
@@ -11550,7 +11550,7 @@
         <v>27</v>
       </c>
       <c r="E72">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F72" t="s">
         <v>28</v>
@@ -11573,7 +11573,7 @@
         <v>27</v>
       </c>
       <c r="E73">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F73" t="s">
         <v>28</v>
@@ -11596,7 +11596,7 @@
         <v>27</v>
       </c>
       <c r="E74">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -11619,7 +11619,7 @@
         <v>27</v>
       </c>
       <c r="E75">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
@@ -11688,7 +11688,7 @@
         <v>27</v>
       </c>
       <c r="E78">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
@@ -11711,7 +11711,7 @@
         <v>27</v>
       </c>
       <c r="E79">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="E80">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
@@ -11757,7 +11757,7 @@
         <v>27</v>
       </c>
       <c r="E81">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c r="E82">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
@@ -11803,7 +11803,7 @@
         <v>27</v>
       </c>
       <c r="E83">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
@@ -11826,7 +11826,7 @@
         <v>27</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
@@ -11849,7 +11849,7 @@
         <v>27</v>
       </c>
       <c r="E85">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
@@ -11872,7 +11872,7 @@
         <v>27</v>
       </c>
       <c r="E86">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F86" t="s">
         <v>28</v>
@@ -11895,7 +11895,7 @@
         <v>27</v>
       </c>
       <c r="E87">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
@@ -11918,7 +11918,7 @@
         <v>27</v>
       </c>
       <c r="E88">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
@@ -11941,7 +11941,7 @@
         <v>27</v>
       </c>
       <c r="E89">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
@@ -11964,7 +11964,7 @@
         <v>27</v>
       </c>
       <c r="E90">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
@@ -11987,7 +11987,7 @@
         <v>27</v>
       </c>
       <c r="E91">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
@@ -12010,7 +12010,7 @@
         <v>27</v>
       </c>
       <c r="E92">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
@@ -12033,7 +12033,7 @@
         <v>27</v>
       </c>
       <c r="E93">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
@@ -12056,7 +12056,7 @@
         <v>27</v>
       </c>
       <c r="E94">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
@@ -12079,7 +12079,7 @@
         <v>27</v>
       </c>
       <c r="E95">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
@@ -12102,7 +12102,7 @@
         <v>27</v>
       </c>
       <c r="E96">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
@@ -12125,7 +12125,7 @@
         <v>27</v>
       </c>
       <c r="E97">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
@@ -12148,7 +12148,7 @@
         <v>27</v>
       </c>
       <c r="E98">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
@@ -12171,7 +12171,7 @@
         <v>27</v>
       </c>
       <c r="E99">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
@@ -12194,7 +12194,7 @@
         <v>27</v>
       </c>
       <c r="E100">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
@@ -12217,7 +12217,7 @@
         <v>27</v>
       </c>
       <c r="E101">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
@@ -12240,7 +12240,7 @@
         <v>27</v>
       </c>
       <c r="E102">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
@@ -12263,7 +12263,7 @@
         <v>27</v>
       </c>
       <c r="E103">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
@@ -12286,7 +12286,7 @@
         <v>27</v>
       </c>
       <c r="E104">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
@@ -12309,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="E105">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="E106">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
@@ -12355,7 +12355,7 @@
         <v>27</v>
       </c>
       <c r="E107">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
@@ -12378,7 +12378,7 @@
         <v>27</v>
       </c>
       <c r="E108">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
@@ -12401,7 +12401,7 @@
         <v>27</v>
       </c>
       <c r="E109">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
@@ -12424,7 +12424,7 @@
         <v>27</v>
       </c>
       <c r="E110">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
@@ -12470,7 +12470,7 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F112" t="s">
         <v>28</v>
@@ -12493,7 +12493,7 @@
         <v>27</v>
       </c>
       <c r="E113">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F113" t="s">
         <v>28</v>
@@ -12516,7 +12516,7 @@
         <v>27</v>
       </c>
       <c r="E114">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F114" t="s">
         <v>28</v>
@@ -12539,7 +12539,7 @@
         <v>27</v>
       </c>
       <c r="E115">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F115" t="s">
         <v>28</v>
@@ -12562,7 +12562,7 @@
         <v>27</v>
       </c>
       <c r="E116">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F116" t="s">
         <v>28</v>
@@ -12585,7 +12585,7 @@
         <v>27</v>
       </c>
       <c r="E117">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
@@ -12608,7 +12608,7 @@
         <v>27</v>
       </c>
       <c r="E118">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
@@ -12631,7 +12631,7 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
@@ -12654,7 +12654,7 @@
         <v>27</v>
       </c>
       <c r="E120">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
@@ -12677,7 +12677,7 @@
         <v>27</v>
       </c>
       <c r="E121">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
@@ -12723,7 +12723,7 @@
         <v>27</v>
       </c>
       <c r="E123">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
@@ -12746,7 +12746,7 @@
         <v>27</v>
       </c>
       <c r="E124">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
@@ -12769,7 +12769,7 @@
         <v>27</v>
       </c>
       <c r="E125">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
@@ -12792,7 +12792,7 @@
         <v>27</v>
       </c>
       <c r="E126">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
@@ -12815,7 +12815,7 @@
         <v>27</v>
       </c>
       <c r="E127">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
@@ -12838,7 +12838,7 @@
         <v>27</v>
       </c>
       <c r="E128">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
@@ -12861,7 +12861,7 @@
         <v>27</v>
       </c>
       <c r="E129">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
@@ -12884,7 +12884,7 @@
         <v>27</v>
       </c>
       <c r="E130">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
@@ -12907,7 +12907,7 @@
         <v>27</v>
       </c>
       <c r="E131">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="E132">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
@@ -12953,7 +12953,7 @@
         <v>27</v>
       </c>
       <c r="E133">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
@@ -12976,7 +12976,7 @@
         <v>27</v>
       </c>
       <c r="E134">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
@@ -12999,7 +12999,7 @@
         <v>27</v>
       </c>
       <c r="E135">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
@@ -13022,7 +13022,7 @@
         <v>27</v>
       </c>
       <c r="E136">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
@@ -13045,7 +13045,7 @@
         <v>27</v>
       </c>
       <c r="E137">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
@@ -13068,7 +13068,7 @@
         <v>27</v>
       </c>
       <c r="E138">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
@@ -13091,7 +13091,7 @@
         <v>27</v>
       </c>
       <c r="E139">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
@@ -13114,7 +13114,7 @@
         <v>27</v>
       </c>
       <c r="E140">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
@@ -13137,7 +13137,7 @@
         <v>27</v>
       </c>
       <c r="E141">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
@@ -13160,7 +13160,7 @@
         <v>27</v>
       </c>
       <c r="E142">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F142" t="s">
         <v>28</v>
@@ -13183,7 +13183,7 @@
         <v>27</v>
       </c>
       <c r="E143">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -13206,7 +13206,7 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F144" t="s">
         <v>28</v>
@@ -13229,7 +13229,7 @@
         <v>27</v>
       </c>
       <c r="E145">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F145" t="s">
         <v>28</v>
@@ -13252,7 +13252,7 @@
         <v>27</v>
       </c>
       <c r="E146">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F146" t="s">
         <v>28</v>
@@ -13275,7 +13275,7 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
@@ -13298,7 +13298,7 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
@@ -13321,7 +13321,7 @@
         <v>27</v>
       </c>
       <c r="E149">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
@@ -13344,7 +13344,7 @@
         <v>27</v>
       </c>
       <c r="E150">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
@@ -13367,7 +13367,7 @@
         <v>27</v>
       </c>
       <c r="E151">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
@@ -13390,7 +13390,7 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F152" t="s">
         <v>28</v>
@@ -13413,7 +13413,7 @@
         <v>27</v>
       </c>
       <c r="E153">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F153" t="s">
         <v>28</v>
@@ -13436,7 +13436,7 @@
         <v>27</v>
       </c>
       <c r="E154">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F154" t="s">
         <v>28</v>
@@ -13459,7 +13459,7 @@
         <v>27</v>
       </c>
       <c r="E155">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F155" t="s">
         <v>28</v>
@@ -13482,7 +13482,7 @@
         <v>27</v>
       </c>
       <c r="E156">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F156" t="s">
         <v>28</v>
@@ -13505,7 +13505,7 @@
         <v>27</v>
       </c>
       <c r="E157">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F157" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="E158">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F158" t="s">
         <v>28</v>
@@ -13551,7 +13551,7 @@
         <v>27</v>
       </c>
       <c r="E159">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F159" t="s">
         <v>28</v>
@@ -13574,7 +13574,7 @@
         <v>27</v>
       </c>
       <c r="E160">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F160" t="s">
         <v>28</v>
@@ -13597,7 +13597,7 @@
         <v>27</v>
       </c>
       <c r="E161">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F161" t="s">
         <v>28</v>
@@ -13620,7 +13620,7 @@
         <v>27</v>
       </c>
       <c r="E162">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
@@ -13643,7 +13643,7 @@
         <v>27</v>
       </c>
       <c r="E163">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
@@ -13666,7 +13666,7 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
@@ -13689,7 +13689,7 @@
         <v>27</v>
       </c>
       <c r="E165">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
@@ -13712,7 +13712,7 @@
         <v>27</v>
       </c>
       <c r="E166">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
@@ -13735,7 +13735,7 @@
         <v>27</v>
       </c>
       <c r="E167">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
@@ -13758,7 +13758,7 @@
         <v>27</v>
       </c>
       <c r="E168">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
@@ -13781,7 +13781,7 @@
         <v>27</v>
       </c>
       <c r="E169">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
@@ -13804,7 +13804,7 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
@@ -13827,7 +13827,7 @@
         <v>27</v>
       </c>
       <c r="E171">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
@@ -13850,7 +13850,7 @@
         <v>27</v>
       </c>
       <c r="E172">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
@@ -13873,7 +13873,7 @@
         <v>27</v>
       </c>
       <c r="E173">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
@@ -13896,7 +13896,7 @@
         <v>27</v>
       </c>
       <c r="E174">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
@@ -13919,7 +13919,7 @@
         <v>27</v>
       </c>
       <c r="E175">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
@@ -13942,7 +13942,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
@@ -13965,7 +13965,7 @@
         <v>27</v>
       </c>
       <c r="E177">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
@@ -13988,7 +13988,7 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
@@ -14011,7 +14011,7 @@
         <v>27</v>
       </c>
       <c r="E179">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
@@ -14034,7 +14034,7 @@
         <v>27</v>
       </c>
       <c r="E180">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
@@ -14057,7 +14057,7 @@
         <v>27</v>
       </c>
       <c r="E181">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
@@ -14080,7 +14080,7 @@
         <v>27</v>
       </c>
       <c r="E182">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F182" t="s">
         <v>28</v>
@@ -14103,7 +14103,7 @@
         <v>27</v>
       </c>
       <c r="E183">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F183" t="s">
         <v>28</v>
@@ -14126,7 +14126,7 @@
         <v>27</v>
       </c>
       <c r="E184">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F184" t="s">
         <v>28</v>
@@ -14149,7 +14149,7 @@
         <v>27</v>
       </c>
       <c r="E185">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F185" t="s">
         <v>28</v>
@@ -14172,7 +14172,7 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F186" t="s">
         <v>28</v>
@@ -14195,7 +14195,7 @@
         <v>27</v>
       </c>
       <c r="E187">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F187" t="s">
         <v>28</v>
@@ -14218,7 +14218,7 @@
         <v>27</v>
       </c>
       <c r="E188">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F188" t="s">
         <v>28</v>
@@ -14241,7 +14241,7 @@
         <v>27</v>
       </c>
       <c r="E189">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F189" t="s">
         <v>28</v>
@@ -14264,7 +14264,7 @@
         <v>27</v>
       </c>
       <c r="E190">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F190" t="s">
         <v>28</v>
@@ -14287,7 +14287,7 @@
         <v>27</v>
       </c>
       <c r="E191">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F191" t="s">
         <v>28</v>
@@ -14310,7 +14310,7 @@
         <v>27</v>
       </c>
       <c r="E192">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
@@ -14333,7 +14333,7 @@
         <v>27</v>
       </c>
       <c r="E193">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
@@ -14356,7 +14356,7 @@
         <v>27</v>
       </c>
       <c r="E194">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
@@ -14379,7 +14379,7 @@
         <v>27</v>
       </c>
       <c r="E195">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
@@ -14402,7 +14402,7 @@
         <v>27</v>
       </c>
       <c r="E196">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
@@ -14425,7 +14425,7 @@
         <v>27</v>
       </c>
       <c r="E197">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F197" t="s">
         <v>28</v>
@@ -14448,7 +14448,7 @@
         <v>27</v>
       </c>
       <c r="E198">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F198" t="s">
         <v>28</v>
@@ -14471,7 +14471,7 @@
         <v>27</v>
       </c>
       <c r="E199">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F199" t="s">
         <v>28</v>
@@ -14494,7 +14494,7 @@
         <v>27</v>
       </c>
       <c r="E200">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F200" t="s">
         <v>28</v>
@@ -14517,7 +14517,7 @@
         <v>27</v>
       </c>
       <c r="E201">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F201" t="s">
         <v>28</v>
@@ -14540,7 +14540,7 @@
         <v>27</v>
       </c>
       <c r="E202">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
@@ -14563,7 +14563,7 @@
         <v>27</v>
       </c>
       <c r="E203">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
@@ -14586,7 +14586,7 @@
         <v>27</v>
       </c>
       <c r="E204">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
@@ -14632,7 +14632,7 @@
         <v>27</v>
       </c>
       <c r="E206">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
@@ -14655,7 +14655,7 @@
         <v>27</v>
       </c>
       <c r="E207">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
@@ -14678,7 +14678,7 @@
         <v>27</v>
       </c>
       <c r="E208">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
@@ -14701,7 +14701,7 @@
         <v>27</v>
       </c>
       <c r="E209">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
@@ -14724,7 +14724,7 @@
         <v>27</v>
       </c>
       <c r="E210">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
@@ -14747,7 +14747,7 @@
         <v>27</v>
       </c>
       <c r="E211">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
@@ -14770,7 +14770,7 @@
         <v>27</v>
       </c>
       <c r="E212">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F212" t="s">
         <v>28</v>
@@ -14793,7 +14793,7 @@
         <v>27</v>
       </c>
       <c r="E213">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F213" t="s">
         <v>28</v>
@@ -14816,7 +14816,7 @@
         <v>27</v>
       </c>
       <c r="E214">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F214" t="s">
         <v>28</v>
@@ -14839,7 +14839,7 @@
         <v>27</v>
       </c>
       <c r="E215">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F215" t="s">
         <v>28</v>
@@ -14862,7 +14862,7 @@
         <v>27</v>
       </c>
       <c r="E216">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F216" t="s">
         <v>28</v>
@@ -14885,7 +14885,7 @@
         <v>27</v>
       </c>
       <c r="E217">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F217" t="s">
         <v>28</v>
@@ -14908,7 +14908,7 @@
         <v>27</v>
       </c>
       <c r="E218">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F218" t="s">
         <v>28</v>
@@ -14931,7 +14931,7 @@
         <v>27</v>
       </c>
       <c r="E219">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F219" t="s">
         <v>28</v>
@@ -14954,7 +14954,7 @@
         <v>27</v>
       </c>
       <c r="E220">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F220" t="s">
         <v>28</v>
@@ -14977,7 +14977,7 @@
         <v>27</v>
       </c>
       <c r="E221">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F221" t="s">
         <v>28</v>
@@ -15000,7 +15000,7 @@
         <v>27</v>
       </c>
       <c r="E222">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F222" t="s">
         <v>28</v>
@@ -15023,7 +15023,7 @@
         <v>27</v>
       </c>
       <c r="E223">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F223" t="s">
         <v>28</v>
@@ -15046,7 +15046,7 @@
         <v>27</v>
       </c>
       <c r="E224">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F224" t="s">
         <v>28</v>
@@ -15069,7 +15069,7 @@
         <v>27</v>
       </c>
       <c r="E225">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F225" t="s">
         <v>28</v>
@@ -15092,7 +15092,7 @@
         <v>27</v>
       </c>
       <c r="E226">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F226" t="s">
         <v>28</v>
@@ -15115,7 +15115,7 @@
         <v>27</v>
       </c>
       <c r="E227">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F227" t="s">
         <v>28</v>
@@ -15138,7 +15138,7 @@
         <v>27</v>
       </c>
       <c r="E228">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F228" t="s">
         <v>28</v>
@@ -15161,7 +15161,7 @@
         <v>27</v>
       </c>
       <c r="E229">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F229" t="s">
         <v>28</v>
@@ -15184,7 +15184,7 @@
         <v>27</v>
       </c>
       <c r="E230">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F230" t="s">
         <v>28</v>
@@ -15207,7 +15207,7 @@
         <v>27</v>
       </c>
       <c r="E231">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F231" t="s">
         <v>28</v>
@@ -15230,7 +15230,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F232" t="s">
         <v>28</v>
@@ -15253,7 +15253,7 @@
         <v>27</v>
       </c>
       <c r="E233">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F233" t="s">
         <v>28</v>
@@ -15276,7 +15276,7 @@
         <v>27</v>
       </c>
       <c r="E234">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F234" t="s">
         <v>28</v>
@@ -15299,7 +15299,7 @@
         <v>27</v>
       </c>
       <c r="E235">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F235" t="s">
         <v>28</v>
@@ -15322,7 +15322,7 @@
         <v>27</v>
       </c>
       <c r="E236">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F236" t="s">
         <v>28</v>
@@ -15345,7 +15345,7 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F237" t="s">
         <v>28</v>
@@ -15368,7 +15368,7 @@
         <v>27</v>
       </c>
       <c r="E238">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F238" t="s">
         <v>28</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="E239">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F239" t="s">
         <v>28</v>
@@ -15414,7 +15414,7 @@
         <v>27</v>
       </c>
       <c r="E240">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F240" t="s">
         <v>28</v>
@@ -15437,7 +15437,7 @@
         <v>27</v>
       </c>
       <c r="E241">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F241" t="s">
         <v>28</v>
@@ -15460,7 +15460,7 @@
         <v>27</v>
       </c>
       <c r="E242">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F242" t="s">
         <v>28</v>
@@ -15506,7 +15506,7 @@
         <v>27</v>
       </c>
       <c r="E244">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F244" t="s">
         <v>28</v>
@@ -15529,7 +15529,7 @@
         <v>27</v>
       </c>
       <c r="E245">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F245" t="s">
         <v>28</v>
@@ -15552,7 +15552,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F246" t="s">
         <v>28</v>
@@ -15575,7 +15575,7 @@
         <v>27</v>
       </c>
       <c r="E247">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F247" t="s">
         <v>28</v>
@@ -15598,7 +15598,7 @@
         <v>27</v>
       </c>
       <c r="E248">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F248" t="s">
         <v>28</v>
@@ -15621,7 +15621,7 @@
         <v>27</v>
       </c>
       <c r="E249">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F249" t="s">
         <v>28</v>
@@ -15644,7 +15644,7 @@
         <v>27</v>
       </c>
       <c r="E250">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F250" t="s">
         <v>28</v>
@@ -15667,7 +15667,7 @@
         <v>27</v>
       </c>
       <c r="E251">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F251" t="s">
         <v>28</v>
@@ -15690,7 +15690,7 @@
         <v>27</v>
       </c>
       <c r="E252">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F252" t="s">
         <v>28</v>
@@ -15713,7 +15713,7 @@
         <v>27</v>
       </c>
       <c r="E253">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F253" t="s">
         <v>28</v>
@@ -15736,7 +15736,7 @@
         <v>27</v>
       </c>
       <c r="E254">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F254" t="s">
         <v>28</v>
@@ -15759,7 +15759,7 @@
         <v>27</v>
       </c>
       <c r="E255">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F255" t="s">
         <v>28</v>
@@ -15782,7 +15782,7 @@
         <v>27</v>
       </c>
       <c r="E256">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F256" t="s">
         <v>28</v>
@@ -15805,7 +15805,7 @@
         <v>27</v>
       </c>
       <c r="E257">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F257" t="s">
         <v>28</v>
@@ -15828,7 +15828,7 @@
         <v>27</v>
       </c>
       <c r="E258">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -15851,7 +15851,7 @@
         <v>27</v>
       </c>
       <c r="E259">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -15874,7 +15874,7 @@
         <v>27</v>
       </c>
       <c r="E260">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -15897,7 +15897,7 @@
         <v>27</v>
       </c>
       <c r="E261">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -15920,7 +15920,7 @@
         <v>27</v>
       </c>
       <c r="E262">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -15943,7 +15943,7 @@
         <v>27</v>
       </c>
       <c r="E263">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -15966,7 +15966,7 @@
         <v>27</v>
       </c>
       <c r="E264">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -15989,7 +15989,7 @@
         <v>27</v>
       </c>
       <c r="E265">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -16012,7 +16012,7 @@
         <v>27</v>
       </c>
       <c r="E266">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -16035,7 +16035,7 @@
         <v>27</v>
       </c>
       <c r="E267">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F267" t="s">
         <v>28</v>
@@ -16058,7 +16058,7 @@
         <v>27</v>
       </c>
       <c r="E268">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F268" t="s">
         <v>28</v>
@@ -16081,7 +16081,7 @@
         <v>27</v>
       </c>
       <c r="E269">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F269" t="s">
         <v>28</v>
@@ -16104,7 +16104,7 @@
         <v>27</v>
       </c>
       <c r="E270">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F270" t="s">
         <v>28</v>
@@ -16127,7 +16127,7 @@
         <v>27</v>
       </c>
       <c r="E271">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F271" t="s">
         <v>28</v>
@@ -16150,7 +16150,7 @@
         <v>27</v>
       </c>
       <c r="E272">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F272" t="s">
         <v>28</v>
@@ -16173,7 +16173,7 @@
         <v>27</v>
       </c>
       <c r="E273">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F273" t="s">
         <v>28</v>
@@ -16196,7 +16196,7 @@
         <v>27</v>
       </c>
       <c r="E274">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F274" t="s">
         <v>28</v>
@@ -16219,7 +16219,7 @@
         <v>27</v>
       </c>
       <c r="E275">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F275" t="s">
         <v>28</v>
@@ -16242,7 +16242,7 @@
         <v>27</v>
       </c>
       <c r="E276">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F276" t="s">
         <v>28</v>
@@ -16265,7 +16265,7 @@
         <v>27</v>
       </c>
       <c r="E277">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F277" t="s">
         <v>28</v>
@@ -16288,7 +16288,7 @@
         <v>27</v>
       </c>
       <c r="E278">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F278" t="s">
         <v>28</v>
@@ -16311,7 +16311,7 @@
         <v>27</v>
       </c>
       <c r="E279">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F279" t="s">
         <v>28</v>
@@ -16334,7 +16334,7 @@
         <v>27</v>
       </c>
       <c r="E280">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F280" t="s">
         <v>28</v>
@@ -16357,7 +16357,7 @@
         <v>27</v>
       </c>
       <c r="E281">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F281" t="s">
         <v>28</v>
@@ -16380,7 +16380,7 @@
         <v>27</v>
       </c>
       <c r="E282">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F282" t="s">
         <v>28</v>
@@ -16403,7 +16403,7 @@
         <v>27</v>
       </c>
       <c r="E283">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F283" t="s">
         <v>28</v>
@@ -16426,7 +16426,7 @@
         <v>27</v>
       </c>
       <c r="E284">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F284" t="s">
         <v>28</v>
@@ -16449,7 +16449,7 @@
         <v>27</v>
       </c>
       <c r="E285">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F285" t="s">
         <v>28</v>
@@ -16472,7 +16472,7 @@
         <v>27</v>
       </c>
       <c r="E286">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F286" t="s">
         <v>28</v>
@@ -16495,7 +16495,7 @@
         <v>27</v>
       </c>
       <c r="E287">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F287" t="s">
         <v>28</v>
@@ -16518,7 +16518,7 @@
         <v>27</v>
       </c>
       <c r="E288">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F288" t="s">
         <v>28</v>
@@ -16541,7 +16541,7 @@
         <v>27</v>
       </c>
       <c r="E289">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F289" t="s">
         <v>28</v>
@@ -16564,7 +16564,7 @@
         <v>27</v>
       </c>
       <c r="E290">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F290" t="s">
         <v>28</v>
@@ -16587,7 +16587,7 @@
         <v>27</v>
       </c>
       <c r="E291">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F291" t="s">
         <v>28</v>
@@ -16610,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="E292">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F292" t="s">
         <v>28</v>
@@ -16633,7 +16633,7 @@
         <v>27</v>
       </c>
       <c r="E293">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F293" t="s">
         <v>28</v>
@@ -16656,7 +16656,7 @@
         <v>27</v>
       </c>
       <c r="E294">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F294" t="s">
         <v>28</v>
@@ -16702,7 +16702,7 @@
         <v>27</v>
       </c>
       <c r="E296">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F296" t="s">
         <v>28</v>
@@ -16725,7 +16725,7 @@
         <v>27</v>
       </c>
       <c r="E297">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F297" t="s">
         <v>28</v>
@@ -16748,7 +16748,7 @@
         <v>27</v>
       </c>
       <c r="E298">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F298" t="s">
         <v>28</v>
@@ -16771,7 +16771,7 @@
         <v>27</v>
       </c>
       <c r="E299">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F299" t="s">
         <v>28</v>
@@ -16794,7 +16794,7 @@
         <v>27</v>
       </c>
       <c r="E300">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F300" t="s">
         <v>28</v>
@@ -16817,7 +16817,7 @@
         <v>27</v>
       </c>
       <c r="E301">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F301" t="s">
         <v>28</v>
@@ -16840,7 +16840,7 @@
         <v>27</v>
       </c>
       <c r="E302">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F302" t="s">
         <v>28</v>
@@ -16863,7 +16863,7 @@
         <v>27</v>
       </c>
       <c r="E303">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F303" t="s">
         <v>28</v>
@@ -16886,7 +16886,7 @@
         <v>27</v>
       </c>
       <c r="E304">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F304" t="s">
         <v>28</v>
@@ -16909,7 +16909,7 @@
         <v>27</v>
       </c>
       <c r="E305">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F305" t="s">
         <v>28</v>
@@ -16932,7 +16932,7 @@
         <v>27</v>
       </c>
       <c r="E306">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F306" t="s">
         <v>28</v>
@@ -16955,7 +16955,7 @@
         <v>27</v>
       </c>
       <c r="E307">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F307" t="s">
         <v>28</v>
@@ -16978,7 +16978,7 @@
         <v>27</v>
       </c>
       <c r="E308">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F308" t="s">
         <v>28</v>
@@ -17001,7 +17001,7 @@
         <v>27</v>
       </c>
       <c r="E309">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F309" t="s">
         <v>28</v>
@@ -17024,7 +17024,7 @@
         <v>27</v>
       </c>
       <c r="E310">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F310" t="s">
         <v>28</v>
@@ -17047,7 +17047,7 @@
         <v>27</v>
       </c>
       <c r="E311">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F311" t="s">
         <v>28</v>
@@ -17070,7 +17070,7 @@
         <v>27</v>
       </c>
       <c r="E312">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F312" t="s">
         <v>28</v>
@@ -17093,7 +17093,7 @@
         <v>27</v>
       </c>
       <c r="E313">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F313" t="s">
         <v>28</v>
@@ -17116,7 +17116,7 @@
         <v>27</v>
       </c>
       <c r="E314">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F314" t="s">
         <v>28</v>
@@ -17139,7 +17139,7 @@
         <v>27</v>
       </c>
       <c r="E315">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F315" t="s">
         <v>28</v>
@@ -17162,7 +17162,7 @@
         <v>27</v>
       </c>
       <c r="E316">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F316" t="s">
         <v>28</v>
@@ -17185,7 +17185,7 @@
         <v>27</v>
       </c>
       <c r="E317">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F317" t="s">
         <v>28</v>
@@ -17208,7 +17208,7 @@
         <v>27</v>
       </c>
       <c r="E318">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F318" t="s">
         <v>28</v>
@@ -17231,7 +17231,7 @@
         <v>27</v>
       </c>
       <c r="E319">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F319" t="s">
         <v>28</v>
@@ -17254,7 +17254,7 @@
         <v>27</v>
       </c>
       <c r="E320">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F320" t="s">
         <v>28</v>
@@ -17277,7 +17277,7 @@
         <v>27</v>
       </c>
       <c r="E321">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F321" t="s">
         <v>28</v>
@@ -17300,7 +17300,7 @@
         <v>27</v>
       </c>
       <c r="E322">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F322" t="s">
         <v>28</v>
@@ -17323,7 +17323,7 @@
         <v>27</v>
       </c>
       <c r="E323">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F323" t="s">
         <v>28</v>
@@ -17346,7 +17346,7 @@
         <v>27</v>
       </c>
       <c r="E324">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F324" t="s">
         <v>28</v>
@@ -17369,7 +17369,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F325" t="s">
         <v>28</v>
@@ -17392,7 +17392,7 @@
         <v>27</v>
       </c>
       <c r="E326">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F326" t="s">
         <v>28</v>
@@ -17415,7 +17415,7 @@
         <v>27</v>
       </c>
       <c r="E327">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F327" t="s">
         <v>28</v>
@@ -17438,7 +17438,7 @@
         <v>27</v>
       </c>
       <c r="E328">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F328" t="s">
         <v>28</v>
@@ -17461,7 +17461,7 @@
         <v>27</v>
       </c>
       <c r="E329">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F329" t="s">
         <v>28</v>
@@ -17484,7 +17484,7 @@
         <v>27</v>
       </c>
       <c r="E330">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F330" t="s">
         <v>28</v>
@@ -17507,7 +17507,7 @@
         <v>27</v>
       </c>
       <c r="E331">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F331" t="s">
         <v>28</v>
@@ -17530,7 +17530,7 @@
         <v>27</v>
       </c>
       <c r="E332">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F332" t="s">
         <v>28</v>
@@ -17553,7 +17553,7 @@
         <v>27</v>
       </c>
       <c r="E333">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F333" t="s">
         <v>28</v>
@@ -17576,7 +17576,7 @@
         <v>27</v>
       </c>
       <c r="E334">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F334" t="s">
         <v>28</v>
@@ -17599,7 +17599,7 @@
         <v>27</v>
       </c>
       <c r="E335">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F335" t="s">
         <v>28</v>
@@ -17622,7 +17622,7 @@
         <v>27</v>
       </c>
       <c r="E336">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F336" t="s">
         <v>28</v>
@@ -17645,7 +17645,7 @@
         <v>27</v>
       </c>
       <c r="E337">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F337" t="s">
         <v>28</v>
@@ -17668,7 +17668,7 @@
         <v>27</v>
       </c>
       <c r="E338">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F338" t="s">
         <v>28</v>
@@ -17691,7 +17691,7 @@
         <v>27</v>
       </c>
       <c r="E339">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F339" t="s">
         <v>28</v>
@@ -17714,7 +17714,7 @@
         <v>27</v>
       </c>
       <c r="E340">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F340" t="s">
         <v>28</v>
@@ -17737,7 +17737,7 @@
         <v>27</v>
       </c>
       <c r="E341">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F341" t="s">
         <v>28</v>
@@ -17760,7 +17760,7 @@
         <v>27</v>
       </c>
       <c r="E342">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F342" t="s">
         <v>28</v>
@@ -17783,7 +17783,7 @@
         <v>27</v>
       </c>
       <c r="E343">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F343" t="s">
         <v>28</v>
@@ -17806,7 +17806,7 @@
         <v>27</v>
       </c>
       <c r="E344">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F344" t="s">
         <v>28</v>
@@ -17829,7 +17829,7 @@
         <v>27</v>
       </c>
       <c r="E345">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F345" t="s">
         <v>28</v>
@@ -17852,7 +17852,7 @@
         <v>27</v>
       </c>
       <c r="E346">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F346" t="s">
         <v>28</v>
@@ -17875,7 +17875,7 @@
         <v>27</v>
       </c>
       <c r="E347">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F347" t="s">
         <v>28</v>
@@ -17898,7 +17898,7 @@
         <v>27</v>
       </c>
       <c r="E348">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F348" t="s">
         <v>28</v>
@@ -17921,7 +17921,7 @@
         <v>27</v>
       </c>
       <c r="E349">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F349" t="s">
         <v>28</v>
@@ -17967,7 +17967,7 @@
         <v>27</v>
       </c>
       <c r="E351">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F351" t="s">
         <v>28</v>
